--- a/data/remote.xlsx
+++ b/data/remote.xlsx
@@ -1,26 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<s:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <s:workbookPr codeName="ThisWorkbook"/>
-  <s:bookViews>
-    <s:workbookView activeTab="4"/>
-  </s:bookViews>
-  <s:sheets>
-    <s:sheet name="searchMember" sheetId="1" r:id="rId1"/>
-    <s:sheet name="syncUserOrderCode" sheetId="2" r:id="rId2"/>
-    <s:sheet name="getUserVisitTemplates" sheetId="3" r:id="rId3"/>
-    <s:sheet name="saveMemberTemp" sheetId="4" r:id="rId4"/>
-    <s:sheet name="syncEfficacyListInfo" sheetId="5" r:id="rId5"/>
-    <s:sheet name="syncDoctorList" sheetId="6" r:id="rId6"/>
-    <s:sheet name="addAppointmentList" sheetId="7" r:id="rId7"/>
-  </s:sheets>
-  <s:definedNames/>
-  <s:calcPr calcId="124519" fullCalcOnLoad="1"/>
-</s:workbook>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22624"/>
+  <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\Romens_Api_Test\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8475E0CF-2AD0-4550-A440-168A47A65102}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
+  <sheets>
+    <sheet name="searchMember" sheetId="1" r:id="rId1"/>
+    <sheet name="syncUserOrderCode" sheetId="2" r:id="rId2"/>
+    <sheet name="getUserVisitTemplates" sheetId="3" r:id="rId3"/>
+    <sheet name="saveMemberTemp" sheetId="4" r:id="rId4"/>
+    <sheet name="syncEfficacyListInfo" sheetId="5" r:id="rId5"/>
+    <sheet name="syncDoctorList" sheetId="6" r:id="rId6"/>
+    <sheet name="addAppointmentList" sheetId="7" r:id="rId7"/>
+  </sheets>
+  <calcPr calcId="0"/>
+</workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="34">
   <si>
     <t>case_id</t>
   </si>
@@ -127,28 +133,26 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -179,26 +183,34 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf fontId="0" borderId="0" fillId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" builtinId="0" xfId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -464,23 +476,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="13.375" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="17.25" customWidth="1" min="3" max="3"/>
-    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="7.75" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="52.375" customWidth="1" min="6" max="6"/>
-    <col width="31.625" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col min="2" max="2" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.25" customWidth="1"/>
+    <col min="4" max="4" width="8" customWidth="1"/>
+    <col min="5" max="5" width="7.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="52.375" customWidth="1"/>
+    <col min="7" max="7" width="31.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -509,8 +517,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="3" t="n">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" t="s">
@@ -536,30 +544,27 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="18.625" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="19.125" customWidth="1" min="3" max="3"/>
-    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="7.75" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="89.5" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="31.625" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col min="1" max="1" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.125" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="89.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -588,8 +593,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="3" t="n">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" t="s">
@@ -615,29 +620,26 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="20.625" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="26.625" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="7.75" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="86.375" customWidth="1" min="6" max="6"/>
-    <col width="31.625" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col min="1" max="1" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="86.375" customWidth="1"/>
+    <col min="7" max="7" width="31.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -663,8 +665,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="3" t="n">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" t="s">
@@ -690,28 +692,25 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="17.625" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="30.75" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="135.25" customWidth="1" min="6" max="6"/>
-    <col width="31.625" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col min="2" max="2" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="135.25" customWidth="1"/>
+    <col min="7" max="7" width="31.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -740,8 +739,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="156.75" customHeight="1">
-      <c r="A2" s="3" t="n">
+    <row r="2" spans="1:9" ht="156.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" t="s">
@@ -767,27 +766,24 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="17.5" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22.5" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="51.5" customWidth="1" min="6" max="6"/>
-    <col width="31.625" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col min="2" max="2" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="51.5" customWidth="1"/>
+    <col min="7" max="7" width="31.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -816,8 +812,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="3" t="n">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" t="s">
@@ -843,27 +839,24 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="14.125" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22.5" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="99.25" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="31.625" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col min="2" max="2" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="99.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -892,8 +885,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="3" t="n">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" t="s">
@@ -919,28 +912,25 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="17.5" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22.5" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="135.25" customWidth="1" min="6" max="6"/>
-    <col width="31.625" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col min="1" max="1" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="135.25" customWidth="1"/>
+    <col min="7" max="7" width="31.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -969,8 +959,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="3" t="n">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" t="s">
@@ -996,7 +986,8 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
--- a/data/remote.xlsx
+++ b/data/remote.xlsx
@@ -1,32 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22624"/>
-  <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\Romens_Api_Test\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8475E0CF-2AD0-4550-A440-168A47A65102}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
-  <sheets>
-    <sheet name="searchMember" sheetId="1" r:id="rId1"/>
-    <sheet name="syncUserOrderCode" sheetId="2" r:id="rId2"/>
-    <sheet name="getUserVisitTemplates" sheetId="3" r:id="rId3"/>
-    <sheet name="saveMemberTemp" sheetId="4" r:id="rId4"/>
-    <sheet name="syncEfficacyListInfo" sheetId="5" r:id="rId5"/>
-    <sheet name="syncDoctorList" sheetId="6" r:id="rId6"/>
-    <sheet name="addAppointmentList" sheetId="7" r:id="rId7"/>
-  </sheets>
-  <calcPr calcId="0"/>
-</workbook>
+<s:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <s:workbookPr codeName="ThisWorkbook"/>
+  <s:bookViews>
+    <s:workbookView activeTab="0"/>
+  </s:bookViews>
+  <s:sheets>
+    <s:sheet name="searchMember" sheetId="1" r:id="rId1"/>
+    <s:sheet name="syncUserOrderCode" sheetId="2" r:id="rId2"/>
+    <s:sheet name="getUserVisitTemplates" sheetId="3" r:id="rId3"/>
+    <s:sheet name="saveMemberTemp" sheetId="4" r:id="rId4"/>
+    <s:sheet name="syncEfficacyListInfo" sheetId="5" r:id="rId5"/>
+    <s:sheet name="syncDoctorList" sheetId="6" r:id="rId6"/>
+    <s:sheet name="addAppointmentList" sheetId="7" r:id="rId7"/>
+  </s:sheets>
+  <s:definedNames/>
+  <s:calcPr calcId="124519" fullCalcOnLoad="1"/>
+</s:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="34">
   <si>
     <t>case_id</t>
   </si>
@@ -133,26 +127,28 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color rgb="00000000"/>
       <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -183,34 +179,26 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf fontId="0" borderId="0" fillId="0" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" builtinId="0" xfId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -476,19 +464,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
   <cols>
-    <col min="2" max="2" width="13.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.25" customWidth="1"/>
-    <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="7.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="52.375" customWidth="1"/>
-    <col min="7" max="7" width="31.625" bestFit="1" customWidth="1"/>
+    <col width="13.375" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="17.25" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="7.75" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="52.375" customWidth="1" min="6" max="6"/>
+    <col width="31.625" bestFit="1" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -517,8 +509,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="3">
+    <row r="2" spans="1:9">
+      <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="s">
@@ -544,27 +536,30 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.125" customWidth="1"/>
-    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="89.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="31.625" bestFit="1" customWidth="1"/>
+    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="18.625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="19.125" customWidth="1" min="3" max="3"/>
+    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="7.75" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="89.5" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="31.625" bestFit="1" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -593,8 +588,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="3">
+    <row r="2" spans="1:9">
+      <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="s">
@@ -620,26 +615,29 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="86.375" customWidth="1"/>
-    <col min="7" max="7" width="31.625" bestFit="1" customWidth="1"/>
+    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="20.625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="26.625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="7.75" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="86.375" customWidth="1" min="6" max="6"/>
+    <col width="31.625" bestFit="1" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -665,8 +663,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="3">
+    <row r="2" spans="1:8">
+      <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="s">
@@ -692,25 +690,28 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
   <cols>
-    <col min="2" max="2" width="17.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="135.25" customWidth="1"/>
-    <col min="7" max="7" width="31.625" bestFit="1" customWidth="1"/>
+    <col width="17.625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="30.75" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="135.25" customWidth="1" min="6" max="6"/>
+    <col width="31.625" bestFit="1" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -739,8 +740,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="156.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="3">
+    <row r="2" spans="1:9" ht="156.75" customHeight="1">
+      <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="s">
@@ -766,24 +767,27 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
   <cols>
-    <col min="2" max="2" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="51.5" customWidth="1"/>
-    <col min="7" max="7" width="31.625" bestFit="1" customWidth="1"/>
+    <col width="17.5" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="22.5" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="51.5" customWidth="1" min="6" max="6"/>
+    <col width="31.625" bestFit="1" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -812,8 +816,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="3">
+    <row r="2" spans="1:9">
+      <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="s">
@@ -839,24 +843,27 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
   <cols>
-    <col min="2" max="2" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="99.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="31.625" bestFit="1" customWidth="1"/>
+    <col width="14.125" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="22.5" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="99.25" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="31.625" bestFit="1" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -885,8 +892,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="3">
+    <row r="2" spans="1:9">
+      <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="s">
@@ -912,25 +919,28 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="135.25" customWidth="1"/>
-    <col min="7" max="7" width="31.625" bestFit="1" customWidth="1"/>
+    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="17.5" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="22.5" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="135.25" customWidth="1" min="6" max="6"/>
+    <col width="31.625" bestFit="1" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -959,8 +969,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="3">
+    <row r="2" spans="1:9">
+      <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="s">
@@ -986,8 +996,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>